--- a/個人製作_冬/コスト表_井上恋 1.xlsx
+++ b/個人製作_冬/コスト表_井上恋 1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fko2447025\Documents\GitHub\ColorfulFighter5\ColorfulFighter5\個人製作_冬\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fko2447025\Documents\GitHub\ColorfulFighter6\個人製作_冬\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD71FA50-9197-4790-B6FD-1179BF5F50EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC3DDF88-87DD-495F-B4E6-8892DFA5868E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2361,11 +2361,11 @@
       </c>
       <c r="K4" s="2">
         <f ca="1">NETWORKDAYS(K5,K6)</f>
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="L4" s="3">
         <f ca="1" xml:space="preserve"> K3 / K4</f>
-        <v>0.58888888888888891</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="K6" s="1">
         <f ca="1">TODAY()</f>
-        <v>45665</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2470,11 +2470,11 @@
       </c>
       <c r="L9" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K9)</f>
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="M9" s="3">
         <f ca="1">($K$2 - $K$3) / L9</f>
-        <v>-6.5714285714285712</v>
+        <v>-4.1818181818181817</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -2501,11 +2501,11 @@
       </c>
       <c r="L10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K10)</f>
-        <v>8</v>
+        <v>-2</v>
       </c>
       <c r="M10" s="3">
         <f ca="1">($K$2 - $K$3) / L10</f>
-        <v>11.5</v>
+        <v>-46</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2532,11 +2532,11 @@
       </c>
       <c r="L11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),K11)</f>
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="M11" s="3">
         <f ca="1">($K$2 - $K$3) / L11</f>
-        <v>4.8421052631578947</v>
+        <v>8.3636363636363633</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -4086,11 +4086,11 @@
       </c>
       <c r="C5" s="2">
         <f ca="1">NETWORKDAYS(C6,C7)</f>
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D5" s="3">
         <f ca="1" xml:space="preserve"> C4 / C5</f>
-        <v>0.41666666666666669</v>
+        <v>0.35377358490566035</v>
       </c>
     </row>
     <row r="6" spans="2:5">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C7" s="1">
         <f ca="1">TODAY()</f>
-        <v>45665</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="9" spans="2:5">
@@ -4129,11 +4129,11 @@
       </c>
       <c r="D10" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C10)</f>
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="E10" s="3">
         <f ca="1">($C$3 - $C$4) / D10</f>
-        <v>-1.2142857142857142</v>
+        <v>-0.77272727272727271</v>
       </c>
     </row>
     <row r="11" spans="2:5">
@@ -4146,11 +4146,11 @@
       </c>
       <c r="D11" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C11)</f>
-        <v>8</v>
+        <v>-2</v>
       </c>
       <c r="E11" s="3">
         <f ca="1">($C$3 - $C$4) / D11</f>
-        <v>2.125</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -4163,11 +4163,11 @@
       </c>
       <c r="D12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),C12)</f>
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E12" s="3">
         <f ca="1">($C$3 - $C$4) / D12</f>
-        <v>0.89473684210526316</v>
+        <v>1.5454545454545454</v>
       </c>
     </row>
     <row r="18" spans="2:4">
@@ -4423,11 +4423,11 @@
       </c>
       <c r="K7" s="51">
         <f>COUNTIF(H3:H72,J7)</f>
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="L7" s="52">
         <f>K7/K3</f>
-        <v>0.84285714285714286</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8" spans="2:12">
@@ -4454,11 +4454,11 @@
       </c>
       <c r="K8" s="51">
         <f>COUNTIF(H3:H72,J8)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L8" s="42">
         <f>(K8+K9)/K3</f>
-        <v>0.15714285714285714</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9" spans="2:12">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="K9" s="21">
         <f>COUNTIF(H3:H72,J9)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:12">
@@ -5461,7 +5461,7 @@
         <v>0.5</v>
       </c>
       <c r="H57" s="29" t="s">
-        <v>207</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="2:8">
@@ -5481,7 +5481,7 @@
         <v>0.25</v>
       </c>
       <c r="H58" s="29" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="2:8">
@@ -5541,7 +5541,7 @@
         <v>0.5</v>
       </c>
       <c r="H61" s="29" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="62" spans="2:8">
@@ -5561,7 +5561,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="29" t="s">
-        <v>207</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="2:8">
@@ -5792,6 +5792,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="04574505-c322-4981-8ebb-5d25af8d4de8" xsi:nil="true"/>
@@ -5801,15 +5810,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6056,20 +6056,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E02E9DAB-F6A4-45C4-BAF5-BF43C147BB10}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="04574505-c322-4981-8ebb-5d25af8d4de8"/>
     <ds:schemaRef ds:uri="098a3c11-7ac2-46ba-89ce-8b2d5c9f76f8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BF17534-2B47-4857-AC25-7C99424F8AA0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
